--- a/Downloads/TaxES-master/TaxES-master/backend/final/filled_itr.xlsx
+++ b/Downloads/TaxES-master/TaxES-master/backend/final/filled_itr.xlsx
@@ -4893,11 +4893,7 @@
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="391" t="n"/>
       <c r="D7" s="396" t="n"/>
-      <c r="E7" s="400" t="inlineStr">
-        <is>
-          <t>Anjali</t>
-        </is>
-      </c>
+      <c r="E7" s="400" t="n"/>
       <c r="F7" s="401" t="n"/>
       <c r="G7" s="401" t="n"/>
       <c r="H7" s="401" t="n"/>
@@ -4907,7 +4903,7 @@
       <c r="L7" s="401" t="n"/>
       <c r="M7" s="401" t="n"/>
       <c r="N7" s="402" t="n"/>
-      <c r="O7" s="400" t="inlineStr"/>
+      <c r="O7" s="400" t="n"/>
       <c r="P7" s="401" t="n"/>
       <c r="Q7" s="401" t="n"/>
       <c r="R7" s="401" t="n"/>
@@ -4917,7 +4913,7 @@
       <c r="V7" s="401" t="n"/>
       <c r="W7" s="401" t="n"/>
       <c r="X7" s="402" t="n"/>
-      <c r="Y7" s="400" t="inlineStr"/>
+      <c r="Y7" s="400" t="n"/>
       <c r="Z7" s="401" t="n"/>
       <c r="AA7" s="401" t="n"/>
       <c r="AB7" s="401" t="n"/>
@@ -5064,7 +5060,11 @@
       <c r="AK9" s="388" t="n"/>
       <c r="AL9" s="388" t="n"/>
       <c r="AM9" s="389" t="n"/>
-      <c r="AN9" s="404" t="n"/>
+      <c r="AN9" s="404" t="inlineStr">
+        <is>
+          <t>shiv@gmail.com</t>
+        </is>
+      </c>
       <c r="AO9" s="388" t="n"/>
       <c r="AP9" s="388" t="n"/>
       <c r="AQ9" s="388" t="n"/>
@@ -5130,7 +5130,7 @@
       <c r="AM10" s="389" t="n"/>
       <c r="AN10" s="354" t="inlineStr">
         <is>
-          <t xml:space="preserve">Date of Birth (DD/MM/YYYY) </t>
+          <t>7455648569</t>
         </is>
       </c>
       <c r="AO10" s="388" t="n"/>
@@ -5162,11 +5162,7 @@
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="391" t="n"/>
       <c r="D11" s="396" t="n"/>
-      <c r="E11" s="327" t="inlineStr">
-        <is>
-          <t>E - 376</t>
-        </is>
-      </c>
+      <c r="E11" s="327" t="n"/>
       <c r="F11" s="401" t="n"/>
       <c r="G11" s="401" t="n"/>
       <c r="H11" s="401" t="n"/>
@@ -5178,7 +5174,7 @@
       <c r="N11" s="402" t="n"/>
       <c r="O11" s="327" t="inlineStr">
         <is>
-          <t>Ashok Nagar</t>
+          <t>D/O Mukesh Kumar H. No. E - 376 Street No. 15 Ashok Nagar Shahdara Mandoli Saboli North East Delhi - 110093</t>
         </is>
       </c>
       <c r="P11" s="401" t="n"/>
@@ -5320,11 +5316,7 @@
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="391" t="n"/>
       <c r="D13" s="396" t="n"/>
-      <c r="E13" s="327" t="inlineStr">
-        <is>
-          <t>Street No. 15</t>
-        </is>
-      </c>
+      <c r="E13" s="327" t="n"/>
       <c r="F13" s="401" t="n"/>
       <c r="G13" s="401" t="n"/>
       <c r="H13" s="401" t="n"/>
@@ -5342,11 +5334,7 @@
       <c r="T13" s="401" t="n"/>
       <c r="U13" s="401" t="n"/>
       <c r="V13" s="402" t="n"/>
-      <c r="W13" s="327" t="inlineStr">
-        <is>
-          <t>Shahdara Mandoli Saboli</t>
-        </is>
-      </c>
+      <c r="W13" s="327" t="n"/>
       <c r="X13" s="401" t="n"/>
       <c r="Y13" s="401" t="n"/>
       <c r="Z13" s="401" t="n"/>
@@ -5363,11 +5351,7 @@
       <c r="AK13" s="401" t="n"/>
       <c r="AL13" s="401" t="n"/>
       <c r="AM13" s="402" t="n"/>
-      <c r="AN13" s="327" t="inlineStr">
-        <is>
-          <t>North East Delhi</t>
-        </is>
-      </c>
+      <c r="AN13" s="327" t="n"/>
       <c r="AO13" s="401" t="n"/>
       <c r="AP13" s="401" t="n"/>
       <c r="AQ13" s="401" t="n"/>
@@ -5472,7 +5456,7 @@
       <c r="D15" s="396" t="n"/>
       <c r="E15" s="400" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>(Select)</t>
         </is>
       </c>
       <c r="F15" s="401" t="n"/>
@@ -5500,11 +5484,7 @@
       <c r="X15" s="401" t="n"/>
       <c r="Y15" s="401" t="n"/>
       <c r="Z15" s="402" t="n"/>
-      <c r="AA15" s="323" t="inlineStr">
-        <is>
-          <t>110093</t>
-        </is>
-      </c>
+      <c r="AA15" s="323" t="n"/>
       <c r="AB15" s="401" t="n"/>
       <c r="AC15" s="401" t="n"/>
       <c r="AD15" s="402" t="n"/>
@@ -6255,11 +6235,7 @@
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="391" t="n"/>
       <c r="D28" s="396" t="n"/>
-      <c r="E28" s="420" t="inlineStr">
-        <is>
-          <t>stutib19@gmail.com</t>
-        </is>
-      </c>
+      <c r="E28" s="420" t="n"/>
       <c r="F28" s="401" t="n"/>
       <c r="G28" s="401" t="n"/>
       <c r="H28" s="401" t="n"/>
@@ -6273,11 +6249,7 @@
       <c r="P28" s="304" t="n">
         <v>91</v>
       </c>
-      <c r="Q28" s="323" t="inlineStr">
-        <is>
-          <t>9893613300</t>
-        </is>
-      </c>
+      <c r="Q28" s="323" t="n"/>
       <c r="R28" s="401" t="n"/>
       <c r="S28" s="401" t="n"/>
       <c r="T28" s="401" t="n"/>
@@ -7808,7 +7780,7 @@
       <c r="AM52" s="388" t="n"/>
       <c r="AN52" s="389" t="n"/>
       <c r="AO52" s="157" t="n">
-        <v>2377833</v>
+        <v>0</v>
       </c>
       <c r="AP52" s="426" t="n"/>
       <c r="AQ52" s="426" t="n"/>
@@ -7869,7 +7841,7 @@
       <c r="AM53" s="388" t="n"/>
       <c r="AN53" s="389" t="n"/>
       <c r="AO53" s="157" t="n">
-        <v>52400</v>
+        <v>0</v>
       </c>
       <c r="AP53" s="426" t="n"/>
       <c r="AQ53" s="426" t="n"/>
@@ -8242,7 +8214,9 @@
       <c r="AL59" s="388" t="n"/>
       <c r="AM59" s="388" t="n"/>
       <c r="AN59" s="389" t="n"/>
-      <c r="AO59" s="258" t="n"/>
+      <c r="AO59" s="258" t="n">
+        <v>96000</v>
+      </c>
       <c r="AP59" s="401" t="n"/>
       <c r="AQ59" s="401" t="n"/>
       <c r="AR59" s="401" t="n"/>
@@ -8301,7 +8275,9 @@
       <c r="AL60" s="388" t="n"/>
       <c r="AM60" s="388" t="n"/>
       <c r="AN60" s="389" t="n"/>
-      <c r="AO60" s="258" t="n"/>
+      <c r="AO60" s="258" t="n">
+        <v>10000</v>
+      </c>
       <c r="AP60" s="401" t="n"/>
       <c r="AQ60" s="401" t="n"/>
       <c r="AR60" s="401" t="n"/>
@@ -8361,7 +8337,7 @@
       <c r="AM61" s="388" t="n"/>
       <c r="AN61" s="389" t="n"/>
       <c r="AO61" s="157" t="n">
-        <v>0</v>
+        <v>86000</v>
       </c>
       <c r="AP61" s="426" t="n"/>
       <c r="AQ61" s="426" t="n"/>
@@ -8422,7 +8398,7 @@
       <c r="AM62" s="388" t="n"/>
       <c r="AN62" s="389" t="n"/>
       <c r="AO62" s="157" t="n">
-        <v>0</v>
+        <v>25800</v>
       </c>
       <c r="AP62" s="426" t="n"/>
       <c r="AQ62" s="426" t="n"/>
@@ -8483,7 +8459,7 @@
       <c r="AM63" s="388" t="n"/>
       <c r="AN63" s="389" t="n"/>
       <c r="AO63" s="257" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP63" s="426" t="n"/>
       <c r="AQ63" s="426" t="n"/>
@@ -8543,7 +8519,9 @@
       <c r="AL64" s="388" t="n"/>
       <c r="AM64" s="388" t="n"/>
       <c r="AN64" s="389" t="n"/>
-      <c r="AO64" s="258" t="n"/>
+      <c r="AO64" s="258" t="n">
+        <v>2000</v>
+      </c>
       <c r="AP64" s="401" t="n"/>
       <c r="AQ64" s="401" t="n"/>
       <c r="AR64" s="401" t="n"/>
@@ -8604,7 +8582,7 @@
       <c r="AM65" s="388" t="n"/>
       <c r="AN65" s="389" t="n"/>
       <c r="AO65" s="157" t="n">
-        <v>0</v>
+        <v>61200</v>
       </c>
       <c r="AP65" s="426" t="n"/>
       <c r="AQ65" s="426" t="n"/>
@@ -8761,7 +8739,11 @@
       </c>
       <c r="H68" s="388" t="n"/>
       <c r="I68" s="389" t="n"/>
-      <c r="J68" s="430" t="n"/>
+      <c r="J68" s="430" t="inlineStr">
+        <is>
+          <t>Interest Income</t>
+        </is>
+      </c>
       <c r="K68" s="401" t="n"/>
       <c r="L68" s="401" t="n"/>
       <c r="M68" s="401" t="n"/>
@@ -8777,7 +8759,11 @@
       <c r="W68" s="401" t="n"/>
       <c r="X68" s="401" t="n"/>
       <c r="Y68" s="402" t="n"/>
-      <c r="Z68" s="436" t="n"/>
+      <c r="Z68" s="436" t="inlineStr">
+        <is>
+          <t>fghjk</t>
+        </is>
+      </c>
       <c r="AA68" s="401" t="n"/>
       <c r="AB68" s="401" t="n"/>
       <c r="AC68" s="401" t="n"/>
@@ -8792,7 +8778,9 @@
       <c r="AL68" s="401" t="n"/>
       <c r="AM68" s="401" t="n"/>
       <c r="AN68" s="402" t="n"/>
-      <c r="AO68" s="258" t="n"/>
+      <c r="AO68" s="258" t="n">
+        <v>100</v>
+      </c>
       <c r="AP68" s="401" t="n"/>
       <c r="AQ68" s="401" t="n"/>
       <c r="AR68" s="401" t="n"/>
@@ -8835,7 +8823,11 @@
       </c>
       <c r="H69" s="388" t="n"/>
       <c r="I69" s="389" t="n"/>
-      <c r="J69" s="140" t="n"/>
+      <c r="J69" s="140" t="inlineStr">
+        <is>
+          <t>Rental Income</t>
+        </is>
+      </c>
       <c r="K69" s="401" t="n"/>
       <c r="L69" s="401" t="n"/>
       <c r="M69" s="401" t="n"/>
@@ -8851,7 +8843,11 @@
       <c r="W69" s="401" t="n"/>
       <c r="X69" s="401" t="n"/>
       <c r="Y69" s="402" t="n"/>
-      <c r="Z69" s="436" t="n"/>
+      <c r="Z69" s="436" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
       <c r="AA69" s="401" t="n"/>
       <c r="AB69" s="401" t="n"/>
       <c r="AC69" s="401" t="n"/>
@@ -8866,7 +8862,9 @@
       <c r="AL69" s="401" t="n"/>
       <c r="AM69" s="401" t="n"/>
       <c r="AN69" s="402" t="n"/>
-      <c r="AO69" s="258" t="n"/>
+      <c r="AO69" s="258" t="n">
+        <v>8564</v>
+      </c>
       <c r="AP69" s="401" t="n"/>
       <c r="AQ69" s="401" t="n"/>
       <c r="AR69" s="401" t="n"/>
@@ -8909,7 +8907,11 @@
       </c>
       <c r="H70" s="388" t="n"/>
       <c r="I70" s="389" t="n"/>
-      <c r="J70" s="140" t="n"/>
+      <c r="J70" s="140" t="inlineStr">
+        <is>
+          <t>Dividend Income</t>
+        </is>
+      </c>
       <c r="K70" s="401" t="n"/>
       <c r="L70" s="401" t="n"/>
       <c r="M70" s="401" t="n"/>
@@ -8925,7 +8927,11 @@
       <c r="W70" s="401" t="n"/>
       <c r="X70" s="401" t="n"/>
       <c r="Y70" s="402" t="n"/>
-      <c r="Z70" s="436" t="n"/>
+      <c r="Z70" s="436" t="inlineStr">
+        <is>
+          <t>oijhg</t>
+        </is>
+      </c>
       <c r="AA70" s="401" t="n"/>
       <c r="AB70" s="401" t="n"/>
       <c r="AC70" s="401" t="n"/>
@@ -8940,7 +8946,9 @@
       <c r="AL70" s="401" t="n"/>
       <c r="AM70" s="401" t="n"/>
       <c r="AN70" s="402" t="n"/>
-      <c r="AO70" s="258" t="n"/>
+      <c r="AO70" s="258" t="n">
+        <v>452</v>
+      </c>
       <c r="AP70" s="401" t="n"/>
       <c r="AQ70" s="401" t="n"/>
       <c r="AR70" s="401" t="n"/>
@@ -8983,7 +8991,11 @@
       </c>
       <c r="H71" s="388" t="n"/>
       <c r="I71" s="389" t="n"/>
-      <c r="J71" s="140" t="n"/>
+      <c r="J71" s="140" t="inlineStr">
+        <is>
+          <t>Retirement Benefit</t>
+        </is>
+      </c>
       <c r="K71" s="401" t="n"/>
       <c r="L71" s="401" t="n"/>
       <c r="M71" s="401" t="n"/>
@@ -8999,7 +9011,11 @@
       <c r="W71" s="401" t="n"/>
       <c r="X71" s="401" t="n"/>
       <c r="Y71" s="402" t="n"/>
-      <c r="Z71" s="436" t="n"/>
+      <c r="Z71" s="436" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
       <c r="AA71" s="401" t="n"/>
       <c r="AB71" s="401" t="n"/>
       <c r="AC71" s="401" t="n"/>
@@ -9014,7 +9030,9 @@
       <c r="AL71" s="401" t="n"/>
       <c r="AM71" s="401" t="n"/>
       <c r="AN71" s="402" t="n"/>
-      <c r="AO71" s="258" t="n"/>
+      <c r="AO71" s="258" t="n">
+        <v>528</v>
+      </c>
       <c r="AP71" s="401" t="n"/>
       <c r="AQ71" s="401" t="n"/>
       <c r="AR71" s="401" t="n"/>
@@ -10556,7 +10574,7 @@
       <c r="Z96" s="393" t="n"/>
       <c r="AA96" s="394" t="n"/>
       <c r="AB96" s="441" t="n">
-        <v>150000</v>
+        <v>100</v>
       </c>
       <c r="AC96" s="426" t="n"/>
       <c r="AD96" s="426" t="n"/>
@@ -10570,7 +10588,7 @@
       <c r="AL96" s="426" t="n"/>
       <c r="AM96" s="427" t="n"/>
       <c r="AN96" s="226" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="AO96" s="442" t="n"/>
       <c r="AP96" s="442" t="n"/>
@@ -10627,7 +10645,7 @@
       <c r="Z97" s="388" t="n"/>
       <c r="AA97" s="389" t="n"/>
       <c r="AB97" s="259" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AC97" s="388" t="n"/>
       <c r="AD97" s="388" t="n"/>
@@ -10694,7 +10712,7 @@
       <c r="Z98" s="388" t="n"/>
       <c r="AA98" s="389" t="n"/>
       <c r="AB98" s="259" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AC98" s="388" t="n"/>
       <c r="AD98" s="388" t="n"/>
@@ -10761,7 +10779,7 @@
       <c r="Z99" s="388" t="n"/>
       <c r="AA99" s="389" t="n"/>
       <c r="AB99" s="259" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AC99" s="388" t="n"/>
       <c r="AD99" s="388" t="n"/>
@@ -10886,7 +10904,9 @@
       </c>
       <c r="Z101" s="388" t="n"/>
       <c r="AA101" s="389" t="n"/>
-      <c r="AB101" s="258" t="n"/>
+      <c r="AB101" s="258" t="n">
+        <v>500</v>
+      </c>
       <c r="AC101" s="401" t="n"/>
       <c r="AD101" s="401" t="n"/>
       <c r="AE101" s="401" t="n"/>
@@ -11072,7 +11092,7 @@
       <c r="Z104" s="388" t="n"/>
       <c r="AA104" s="389" t="n"/>
       <c r="AB104" s="157" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="AC104" s="426" t="n"/>
       <c r="AD104" s="426" t="n"/>
@@ -11377,7 +11397,7 @@
       <c r="Z108" s="388" t="n"/>
       <c r="AA108" s="389" t="n"/>
       <c r="AB108" s="157" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AC108" s="426" t="n"/>
       <c r="AD108" s="426" t="n"/>
@@ -11456,7 +11476,7 @@
       <c r="Z109" s="386" t="n"/>
       <c r="AA109" s="387" t="n"/>
       <c r="AB109" s="160" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="AC109" s="386" t="n"/>
       <c r="AD109" s="386" t="n"/>
@@ -11582,7 +11602,7 @@
       <c r="Z111" s="388" t="n"/>
       <c r="AA111" s="389" t="n"/>
       <c r="AB111" s="441" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="AC111" s="426" t="n"/>
       <c r="AD111" s="426" t="n"/>
@@ -11649,7 +11669,7 @@
       <c r="Z112" s="388" t="n"/>
       <c r="AA112" s="389" t="n"/>
       <c r="AB112" s="441" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="AC112" s="426" t="n"/>
       <c r="AD112" s="426" t="n"/>
@@ -11850,7 +11870,7 @@
       <c r="Z115" s="388" t="n"/>
       <c r="AA115" s="389" t="n"/>
       <c r="AB115" s="455" t="n">
-        <v>0</v>
+        <v>555</v>
       </c>
       <c r="AC115" s="426" t="n"/>
       <c r="AD115" s="426" t="n"/>
@@ -11917,7 +11937,7 @@
       <c r="Z116" s="388" t="n"/>
       <c r="AA116" s="389" t="n"/>
       <c r="AB116" s="259" t="n">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="AC116" s="388" t="n"/>
       <c r="AD116" s="388" t="n"/>
@@ -12107,7 +12127,7 @@
       <c r="Z119" s="388" t="n"/>
       <c r="AA119" s="389" t="n"/>
       <c r="AB119" s="455" t="n">
-        <v>0</v>
+        <v>21456</v>
       </c>
       <c r="AC119" s="426" t="n"/>
       <c r="AD119" s="426" t="n"/>
@@ -12301,7 +12321,7 @@
       <c r="Z122" s="388" t="n"/>
       <c r="AA122" s="389" t="n"/>
       <c r="AB122" s="160" t="n">
-        <v>0</v>
+        <v>3215</v>
       </c>
       <c r="AC122" s="388" t="n"/>
       <c r="AD122" s="388" t="n"/>
@@ -12443,7 +12463,7 @@
       <c r="Z124" s="388" t="n"/>
       <c r="AA124" s="389" t="n"/>
       <c r="AB124" s="157" t="n">
-        <v>0</v>
+        <v>1235</v>
       </c>
       <c r="AC124" s="426" t="n"/>
       <c r="AD124" s="426" t="n"/>
@@ -12518,7 +12538,7 @@
       <c r="Z125" s="388" t="n"/>
       <c r="AA125" s="389" t="n"/>
       <c r="AB125" s="155" t="n">
-        <v>0</v>
+        <v>3215</v>
       </c>
       <c r="AC125" s="388" t="n"/>
       <c r="AD125" s="388" t="n"/>
@@ -12592,7 +12612,9 @@
       </c>
       <c r="Z126" s="388" t="n"/>
       <c r="AA126" s="389" t="n"/>
-      <c r="AB126" s="155" t="n"/>
+      <c r="AB126" s="155" t="n">
+        <v>0</v>
+      </c>
       <c r="AC126" s="388" t="n"/>
       <c r="AD126" s="388" t="n"/>
       <c r="AE126" s="388" t="n"/>
@@ -13599,7 +13621,7 @@
         <v>10</v>
       </c>
       <c r="AO142" s="462" t="n">
-        <v>465132</v>
+        <v>0</v>
       </c>
       <c r="AP142" s="426" t="n"/>
       <c r="AQ142" s="426" t="n"/>
@@ -13772,7 +13794,7 @@
         <v>12</v>
       </c>
       <c r="AO145" s="466" t="n">
-        <v>483737</v>
+        <v>0</v>
       </c>
       <c r="AP145" s="426" t="n"/>
       <c r="AQ145" s="426" t="n"/>
@@ -13967,7 +13989,7 @@
         <v>14</v>
       </c>
       <c r="AO148" s="157" t="n">
-        <v>483737</v>
+        <v>0</v>
       </c>
       <c r="AP148" s="426" t="n"/>
       <c r="AQ148" s="426" t="n"/>

--- a/Downloads/TaxES-master/TaxES-master/backend/final/filled_itr.xlsx
+++ b/Downloads/TaxES-master/TaxES-master/backend/final/filled_itr.xlsx
@@ -4893,7 +4893,11 @@
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="391" t="n"/>
       <c r="D7" s="396" t="n"/>
-      <c r="E7" s="400" t="n"/>
+      <c r="E7" s="400" t="inlineStr">
+        <is>
+          <t>Shivank</t>
+        </is>
+      </c>
       <c r="F7" s="401" t="n"/>
       <c r="G7" s="401" t="n"/>
       <c r="H7" s="401" t="n"/>
@@ -4903,7 +4907,7 @@
       <c r="L7" s="401" t="n"/>
       <c r="M7" s="401" t="n"/>
       <c r="N7" s="402" t="n"/>
-      <c r="O7" s="400" t="n"/>
+      <c r="O7" s="400" t="inlineStr"/>
       <c r="P7" s="401" t="n"/>
       <c r="Q7" s="401" t="n"/>
       <c r="R7" s="401" t="n"/>
@@ -4913,7 +4917,11 @@
       <c r="V7" s="401" t="n"/>
       <c r="W7" s="401" t="n"/>
       <c r="X7" s="402" t="n"/>
-      <c r="Y7" s="400" t="n"/>
+      <c r="Y7" s="400" t="inlineStr">
+        <is>
+          <t>Rai</t>
+        </is>
+      </c>
       <c r="Z7" s="401" t="n"/>
       <c r="AA7" s="401" t="n"/>
       <c r="AB7" s="401" t="n"/>
@@ -4993,7 +5001,7 @@
       <c r="AM8" s="389" t="n"/>
       <c r="AN8" s="403" t="inlineStr">
         <is>
-          <t>2268 1622 3671</t>
+          <t>3706 8700 5134</t>
         </is>
       </c>
       <c r="AO8" s="401" t="n"/>
@@ -5130,7 +5138,7 @@
       <c r="AM10" s="389" t="n"/>
       <c r="AN10" s="354" t="inlineStr">
         <is>
-          <t>7455648569</t>
+          <t>7455896524</t>
         </is>
       </c>
       <c r="AO10" s="388" t="n"/>
@@ -5162,7 +5170,11 @@
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="391" t="n"/>
       <c r="D11" s="396" t="n"/>
-      <c r="E11" s="327" t="n"/>
+      <c r="E11" s="327" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="F11" s="401" t="n"/>
       <c r="G11" s="401" t="n"/>
       <c r="H11" s="401" t="n"/>
@@ -5174,7 +5186,7 @@
       <c r="N11" s="402" t="n"/>
       <c r="O11" s="327" t="inlineStr">
         <is>
-          <t>D/O Mukesh Kumar H. No. E - 376 Street No. 15 Ashok Nagar Shahdara Mandoli Saboli North East Delhi - 110093</t>
+          <t>Parsvnath Apt</t>
         </is>
       </c>
       <c r="P11" s="401" t="n"/>
@@ -5201,11 +5213,7 @@
       <c r="AK11" s="401" t="n"/>
       <c r="AL11" s="401" t="n"/>
       <c r="AM11" s="402" t="n"/>
-      <c r="AN11" s="400" t="inlineStr">
-        <is>
-          <t>18/09/1999</t>
-        </is>
-      </c>
+      <c r="AN11" s="400" t="n"/>
       <c r="AO11" s="401" t="n"/>
       <c r="AP11" s="401" t="n"/>
       <c r="AQ11" s="401" t="n"/>
@@ -5316,7 +5324,11 @@
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="391" t="n"/>
       <c r="D13" s="396" t="n"/>
-      <c r="E13" s="327" t="n"/>
+      <c r="E13" s="327" t="inlineStr">
+        <is>
+          <t>Amar Singh Marg</t>
+        </is>
+      </c>
       <c r="F13" s="401" t="n"/>
       <c r="G13" s="401" t="n"/>
       <c r="H13" s="401" t="n"/>
@@ -5334,7 +5346,11 @@
       <c r="T13" s="401" t="n"/>
       <c r="U13" s="401" t="n"/>
       <c r="V13" s="402" t="n"/>
-      <c r="W13" s="327" t="n"/>
+      <c r="W13" s="327" t="inlineStr">
+        <is>
+          <t>Freeganj</t>
+        </is>
+      </c>
       <c r="X13" s="401" t="n"/>
       <c r="Y13" s="401" t="n"/>
       <c r="Z13" s="401" t="n"/>
@@ -5351,7 +5367,11 @@
       <c r="AK13" s="401" t="n"/>
       <c r="AL13" s="401" t="n"/>
       <c r="AM13" s="402" t="n"/>
-      <c r="AN13" s="327" t="n"/>
+      <c r="AN13" s="327" t="inlineStr">
+        <is>
+          <t>Ujjain</t>
+        </is>
+      </c>
       <c r="AO13" s="401" t="n"/>
       <c r="AP13" s="401" t="n"/>
       <c r="AQ13" s="401" t="n"/>
@@ -5456,7 +5476,7 @@
       <c r="D15" s="396" t="n"/>
       <c r="E15" s="400" t="inlineStr">
         <is>
-          <t>(Select)</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="F15" s="401" t="n"/>
@@ -5484,7 +5504,11 @@
       <c r="X15" s="401" t="n"/>
       <c r="Y15" s="401" t="n"/>
       <c r="Z15" s="402" t="n"/>
-      <c r="AA15" s="323" t="n"/>
+      <c r="AA15" s="323" t="inlineStr">
+        <is>
+          <t>456010</t>
+        </is>
+      </c>
       <c r="AB15" s="401" t="n"/>
       <c r="AC15" s="401" t="n"/>
       <c r="AD15" s="402" t="n"/>
@@ -8215,7 +8239,7 @@
       <c r="AM59" s="388" t="n"/>
       <c r="AN59" s="389" t="n"/>
       <c r="AO59" s="258" t="n">
-        <v>96000</v>
+        <v>89000</v>
       </c>
       <c r="AP59" s="401" t="n"/>
       <c r="AQ59" s="401" t="n"/>
@@ -8276,7 +8300,7 @@
       <c r="AM60" s="388" t="n"/>
       <c r="AN60" s="389" t="n"/>
       <c r="AO60" s="258" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="AP60" s="401" t="n"/>
       <c r="AQ60" s="401" t="n"/>
@@ -8337,7 +8361,7 @@
       <c r="AM61" s="388" t="n"/>
       <c r="AN61" s="389" t="n"/>
       <c r="AO61" s="157" t="n">
-        <v>86000</v>
+        <v>88000</v>
       </c>
       <c r="AP61" s="426" t="n"/>
       <c r="AQ61" s="426" t="n"/>
@@ -8398,7 +8422,7 @@
       <c r="AM62" s="388" t="n"/>
       <c r="AN62" s="389" t="n"/>
       <c r="AO62" s="157" t="n">
-        <v>25800</v>
+        <v>26400</v>
       </c>
       <c r="AP62" s="426" t="n"/>
       <c r="AQ62" s="426" t="n"/>
@@ -8459,7 +8483,7 @@
       <c r="AM63" s="388" t="n"/>
       <c r="AN63" s="389" t="n"/>
       <c r="AO63" s="257" t="n">
-        <v>1000</v>
+        <v>3200</v>
       </c>
       <c r="AP63" s="426" t="n"/>
       <c r="AQ63" s="426" t="n"/>
@@ -8520,7 +8544,7 @@
       <c r="AM64" s="388" t="n"/>
       <c r="AN64" s="389" t="n"/>
       <c r="AO64" s="258" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="AP64" s="401" t="n"/>
       <c r="AQ64" s="401" t="n"/>
@@ -8582,7 +8606,7 @@
       <c r="AM65" s="388" t="n"/>
       <c r="AN65" s="389" t="n"/>
       <c r="AO65" s="157" t="n">
-        <v>61200</v>
+        <v>64400</v>
       </c>
       <c r="AP65" s="426" t="n"/>
       <c r="AQ65" s="426" t="n"/>
@@ -8761,7 +8785,7 @@
       <c r="Y68" s="402" t="n"/>
       <c r="Z68" s="436" t="inlineStr">
         <is>
-          <t>fghjk</t>
+          <t>sgksjg</t>
         </is>
       </c>
       <c r="AA68" s="401" t="n"/>
@@ -8779,7 +8803,7 @@
       <c r="AM68" s="401" t="n"/>
       <c r="AN68" s="402" t="n"/>
       <c r="AO68" s="258" t="n">
-        <v>100</v>
+        <v>10500</v>
       </c>
       <c r="AP68" s="401" t="n"/>
       <c r="AQ68" s="401" t="n"/>
@@ -8823,11 +8847,7 @@
       </c>
       <c r="H69" s="388" t="n"/>
       <c r="I69" s="389" t="n"/>
-      <c r="J69" s="140" t="inlineStr">
-        <is>
-          <t>Rental Income</t>
-        </is>
-      </c>
+      <c r="J69" s="140" t="inlineStr"/>
       <c r="K69" s="401" t="n"/>
       <c r="L69" s="401" t="n"/>
       <c r="M69" s="401" t="n"/>
@@ -8843,11 +8863,7 @@
       <c r="W69" s="401" t="n"/>
       <c r="X69" s="401" t="n"/>
       <c r="Y69" s="402" t="n"/>
-      <c r="Z69" s="436" t="inlineStr">
-        <is>
-          <t>fghj</t>
-        </is>
-      </c>
+      <c r="Z69" s="436" t="inlineStr"/>
       <c r="AA69" s="401" t="n"/>
       <c r="AB69" s="401" t="n"/>
       <c r="AC69" s="401" t="n"/>
@@ -8863,7 +8879,7 @@
       <c r="AM69" s="401" t="n"/>
       <c r="AN69" s="402" t="n"/>
       <c r="AO69" s="258" t="n">
-        <v>8564</v>
+        <v>0</v>
       </c>
       <c r="AP69" s="401" t="n"/>
       <c r="AQ69" s="401" t="n"/>
@@ -8907,11 +8923,7 @@
       </c>
       <c r="H70" s="388" t="n"/>
       <c r="I70" s="389" t="n"/>
-      <c r="J70" s="140" t="inlineStr">
-        <is>
-          <t>Dividend Income</t>
-        </is>
-      </c>
+      <c r="J70" s="140" t="inlineStr"/>
       <c r="K70" s="401" t="n"/>
       <c r="L70" s="401" t="n"/>
       <c r="M70" s="401" t="n"/>
@@ -8927,11 +8939,7 @@
       <c r="W70" s="401" t="n"/>
       <c r="X70" s="401" t="n"/>
       <c r="Y70" s="402" t="n"/>
-      <c r="Z70" s="436" t="inlineStr">
-        <is>
-          <t>oijhg</t>
-        </is>
-      </c>
+      <c r="Z70" s="436" t="inlineStr"/>
       <c r="AA70" s="401" t="n"/>
       <c r="AB70" s="401" t="n"/>
       <c r="AC70" s="401" t="n"/>
@@ -8947,7 +8955,7 @@
       <c r="AM70" s="401" t="n"/>
       <c r="AN70" s="402" t="n"/>
       <c r="AO70" s="258" t="n">
-        <v>452</v>
+        <v>0</v>
       </c>
       <c r="AP70" s="401" t="n"/>
       <c r="AQ70" s="401" t="n"/>
@@ -8991,11 +8999,7 @@
       </c>
       <c r="H71" s="388" t="n"/>
       <c r="I71" s="389" t="n"/>
-      <c r="J71" s="140" t="inlineStr">
-        <is>
-          <t>Retirement Benefit</t>
-        </is>
-      </c>
+      <c r="J71" s="140" t="inlineStr"/>
       <c r="K71" s="401" t="n"/>
       <c r="L71" s="401" t="n"/>
       <c r="M71" s="401" t="n"/>
@@ -9011,11 +9015,7 @@
       <c r="W71" s="401" t="n"/>
       <c r="X71" s="401" t="n"/>
       <c r="Y71" s="402" t="n"/>
-      <c r="Z71" s="436" t="inlineStr">
-        <is>
-          <t>fghj</t>
-        </is>
-      </c>
+      <c r="Z71" s="436" t="inlineStr"/>
       <c r="AA71" s="401" t="n"/>
       <c r="AB71" s="401" t="n"/>
       <c r="AC71" s="401" t="n"/>
@@ -9031,7 +9031,7 @@
       <c r="AM71" s="401" t="n"/>
       <c r="AN71" s="402" t="n"/>
       <c r="AO71" s="258" t="n">
-        <v>528</v>
+        <v>0</v>
       </c>
       <c r="AP71" s="401" t="n"/>
       <c r="AQ71" s="401" t="n"/>
@@ -10574,7 +10574,7 @@
       <c r="Z96" s="393" t="n"/>
       <c r="AA96" s="394" t="n"/>
       <c r="AB96" s="441" t="n">
-        <v>100</v>
+        <v>110000</v>
       </c>
       <c r="AC96" s="426" t="n"/>
       <c r="AD96" s="426" t="n"/>
@@ -10645,7 +10645,7 @@
       <c r="Z97" s="388" t="n"/>
       <c r="AA97" s="389" t="n"/>
       <c r="AB97" s="259" t="n">
-        <v>200</v>
+        <v>11000</v>
       </c>
       <c r="AC97" s="388" t="n"/>
       <c r="AD97" s="388" t="n"/>
@@ -10712,7 +10712,7 @@
       <c r="Z98" s="388" t="n"/>
       <c r="AA98" s="389" t="n"/>
       <c r="AB98" s="259" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AC98" s="388" t="n"/>
       <c r="AD98" s="388" t="n"/>
@@ -10779,7 +10779,7 @@
       <c r="Z99" s="388" t="n"/>
       <c r="AA99" s="389" t="n"/>
       <c r="AB99" s="259" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AC99" s="388" t="n"/>
       <c r="AD99" s="388" t="n"/>
@@ -10905,7 +10905,7 @@
       <c r="Z101" s="388" t="n"/>
       <c r="AA101" s="389" t="n"/>
       <c r="AB101" s="258" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AC101" s="401" t="n"/>
       <c r="AD101" s="401" t="n"/>
@@ -11092,7 +11092,7 @@
       <c r="Z104" s="388" t="n"/>
       <c r="AA104" s="389" t="n"/>
       <c r="AB104" s="157" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="AC104" s="426" t="n"/>
       <c r="AD104" s="426" t="n"/>
@@ -11397,7 +11397,7 @@
       <c r="Z108" s="388" t="n"/>
       <c r="AA108" s="389" t="n"/>
       <c r="AB108" s="157" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AC108" s="426" t="n"/>
       <c r="AD108" s="426" t="n"/>
@@ -11476,7 +11476,7 @@
       <c r="Z109" s="386" t="n"/>
       <c r="AA109" s="387" t="n"/>
       <c r="AB109" s="160" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="AC109" s="386" t="n"/>
       <c r="AD109" s="386" t="n"/>
@@ -11602,7 +11602,7 @@
       <c r="Z111" s="388" t="n"/>
       <c r="AA111" s="389" t="n"/>
       <c r="AB111" s="441" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="AC111" s="426" t="n"/>
       <c r="AD111" s="426" t="n"/>
@@ -11669,7 +11669,7 @@
       <c r="Z112" s="388" t="n"/>
       <c r="AA112" s="389" t="n"/>
       <c r="AB112" s="441" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="AC112" s="426" t="n"/>
       <c r="AD112" s="426" t="n"/>
@@ -11870,7 +11870,7 @@
       <c r="Z115" s="388" t="n"/>
       <c r="AA115" s="389" t="n"/>
       <c r="AB115" s="455" t="n">
-        <v>555</v>
+        <v>0</v>
       </c>
       <c r="AC115" s="426" t="n"/>
       <c r="AD115" s="426" t="n"/>
@@ -11937,7 +11937,7 @@
       <c r="Z116" s="388" t="n"/>
       <c r="AA116" s="389" t="n"/>
       <c r="AB116" s="259" t="n">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="AC116" s="388" t="n"/>
       <c r="AD116" s="388" t="n"/>
@@ -12127,7 +12127,7 @@
       <c r="Z119" s="388" t="n"/>
       <c r="AA119" s="389" t="n"/>
       <c r="AB119" s="455" t="n">
-        <v>21456</v>
+        <v>0</v>
       </c>
       <c r="AC119" s="426" t="n"/>
       <c r="AD119" s="426" t="n"/>
@@ -12321,7 +12321,7 @@
       <c r="Z122" s="388" t="n"/>
       <c r="AA122" s="389" t="n"/>
       <c r="AB122" s="160" t="n">
-        <v>3215</v>
+        <v>0</v>
       </c>
       <c r="AC122" s="388" t="n"/>
       <c r="AD122" s="388" t="n"/>
@@ -12463,7 +12463,7 @@
       <c r="Z124" s="388" t="n"/>
       <c r="AA124" s="389" t="n"/>
       <c r="AB124" s="157" t="n">
-        <v>1235</v>
+        <v>0</v>
       </c>
       <c r="AC124" s="426" t="n"/>
       <c r="AD124" s="426" t="n"/>
@@ -12538,7 +12538,7 @@
       <c r="Z125" s="388" t="n"/>
       <c r="AA125" s="389" t="n"/>
       <c r="AB125" s="155" t="n">
-        <v>3215</v>
+        <v>0</v>
       </c>
       <c r="AC125" s="388" t="n"/>
       <c r="AD125" s="388" t="n"/>
